--- a/app/Archivos/Template/Template_HRC_olimpica.xlsx
+++ b/app/Archivos/Template/Template_HRC_olimpica.xlsx
@@ -7115,10 +7115,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
-<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
-  <clbl:label id="{89db4e91-bad5-4fd0-9ca4-c06485916e3a}" enabled="1" method="Standard" siteId="{f66fae02-5d36-495b-bfe0-78a6ff9f8e6e}" removed="0"/>
-</clbl:labelList>
 </file>
--- a/app/Archivos/Template/Template_HRC_olimpica.xlsx
+++ b/app/Archivos/Template/Template_HRC_olimpica.xlsx
@@ -786,7 +786,7 @@
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="17" customWidth="1" min="8" max="8"/>
-    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -944,28 +944,24 @@
       </c>
       <c r="D19" s="10" t="inlineStr">
         <is>
-          <t>4633873108</t>
+          <t>85492795</t>
         </is>
       </c>
       <c r="E19" s="6" t="n">
-        <v>-57532</v>
+        <v>-96747</v>
       </c>
       <c r="F19" s="10" t="inlineStr">
         <is>
-          <t>AVERIA</t>
-        </is>
-      </c>
-      <c r="G19" s="10" t="inlineStr">
-        <is>
-          <t>522</t>
-        </is>
-      </c>
+          <t>Descuento</t>
+        </is>
+      </c>
+      <c r="G19" s="10" t="inlineStr"/>
       <c r="H19" s="6" t="n">
-        <v>-57532</v>
+        <v>-96747</v>
       </c>
       <c r="I19" s="11" t="inlineStr">
         <is>
-          <t>AVERIA 4633873108</t>
+          <t>Descuento 85492795</t>
         </is>
       </c>
     </row>
@@ -977,28 +973,24 @@
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>4633966060</t>
+          <t>85492796</t>
         </is>
       </c>
       <c r="E20" s="6" t="n">
-        <v>-7083</v>
+        <v>-400617</v>
       </c>
       <c r="F20" s="10" t="inlineStr">
         <is>
-          <t>AVERIA</t>
-        </is>
-      </c>
-      <c r="G20" s="10" t="inlineStr">
-        <is>
-          <t>522</t>
-        </is>
-      </c>
+          <t>Descuento</t>
+        </is>
+      </c>
+      <c r="G20" s="10" t="inlineStr"/>
       <c r="H20" s="6" t="n">
-        <v>-7083</v>
+        <v>-400617</v>
       </c>
       <c r="I20" s="11" t="inlineStr">
         <is>
-          <t>AVERIA 4633966060</t>
+          <t>Descuento 85492796</t>
         </is>
       </c>
     </row>
@@ -1010,28 +1002,24 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>4634014171</t>
+          <t>85492797</t>
         </is>
       </c>
       <c r="E21" s="6" t="n">
-        <v>-16320</v>
+        <v>-773974</v>
       </c>
       <c r="F21" s="10" t="inlineStr">
         <is>
-          <t>AVERIA</t>
-        </is>
-      </c>
-      <c r="G21" s="10" t="inlineStr">
-        <is>
-          <t>522</t>
-        </is>
-      </c>
+          <t>Descuento</t>
+        </is>
+      </c>
+      <c r="G21" s="10" t="inlineStr"/>
       <c r="H21" s="6" t="n">
-        <v>-16320</v>
+        <v>-773974</v>
       </c>
       <c r="I21" s="11" t="inlineStr">
         <is>
-          <t>AVERIA 4634014171</t>
+          <t>Descuento 85492797</t>
         </is>
       </c>
     </row>
@@ -1043,28 +1031,24 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>4634285011</t>
+          <t>85492798</t>
         </is>
       </c>
       <c r="E22" s="6" t="n">
-        <v>-106845</v>
+        <v>-1762714</v>
       </c>
       <c r="F22" s="10" t="inlineStr">
         <is>
-          <t>AVERIA</t>
-        </is>
-      </c>
-      <c r="G22" s="10" t="inlineStr">
-        <is>
-          <t>522</t>
-        </is>
-      </c>
+          <t>Descuento</t>
+        </is>
+      </c>
+      <c r="G22" s="10" t="inlineStr"/>
       <c r="H22" s="6" t="n">
-        <v>-106845</v>
+        <v>-1762714</v>
       </c>
       <c r="I22" s="11" t="inlineStr">
         <is>
-          <t>AVERIA 4634285011</t>
+          <t>Descuento 85492798</t>
         </is>
       </c>
     </row>
@@ -1076,28 +1060,24 @@
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>4634301618</t>
+          <t>85492799</t>
         </is>
       </c>
       <c r="E23" s="6" t="n">
-        <v>-16809</v>
+        <v>-2515417</v>
       </c>
       <c r="F23" s="10" t="inlineStr">
         <is>
-          <t>AVERIA</t>
-        </is>
-      </c>
-      <c r="G23" s="10" t="inlineStr">
-        <is>
-          <t>522</t>
-        </is>
-      </c>
+          <t>Descuento</t>
+        </is>
+      </c>
+      <c r="G23" s="10" t="inlineStr"/>
       <c r="H23" s="6" t="n">
-        <v>-16809</v>
+        <v>-2515417</v>
       </c>
       <c r="I23" s="11" t="inlineStr">
         <is>
-          <t>AVERIA 4634301618</t>
+          <t>Descuento 85492799</t>
         </is>
       </c>
     </row>
@@ -1109,28 +1089,24 @@
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>4634328866</t>
+          <t>85492800</t>
         </is>
       </c>
       <c r="E24" s="6" t="n">
-        <v>-14166</v>
+        <v>-2902404</v>
       </c>
       <c r="F24" s="10" t="inlineStr">
         <is>
-          <t>AVERIA</t>
-        </is>
-      </c>
-      <c r="G24" s="10" t="inlineStr">
-        <is>
-          <t>522</t>
-        </is>
-      </c>
+          <t>Descuento</t>
+        </is>
+      </c>
+      <c r="G24" s="10" t="inlineStr"/>
       <c r="H24" s="6" t="n">
-        <v>-14166</v>
+        <v>-2902404</v>
       </c>
       <c r="I24" s="11" t="inlineStr">
         <is>
-          <t>AVERIA 4634328866</t>
+          <t>Descuento 85492800</t>
         </is>
       </c>
     </row>
@@ -1142,28 +1118,24 @@
       </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>4634412628</t>
+          <t>85492801</t>
         </is>
       </c>
       <c r="E25" s="6" t="n">
-        <v>-16320</v>
+        <v>-4125942</v>
       </c>
       <c r="F25" s="10" t="inlineStr">
         <is>
-          <t>AVERIA</t>
-        </is>
-      </c>
-      <c r="G25" s="10" t="inlineStr">
-        <is>
-          <t>522</t>
-        </is>
-      </c>
+          <t>Descuento</t>
+        </is>
+      </c>
+      <c r="G25" s="10" t="inlineStr"/>
       <c r="H25" s="6" t="n">
-        <v>-16320</v>
+        <v>-4125942</v>
       </c>
       <c r="I25" s="11" t="inlineStr">
         <is>
-          <t>AVERIA 4634412628</t>
+          <t>Descuento 85492801</t>
         </is>
       </c>
     </row>
@@ -1175,28 +1147,24 @@
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>4634459674</t>
+          <t>85492802</t>
         </is>
       </c>
       <c r="E26" s="6" t="n">
-        <v>-94983</v>
+        <v>-5220427</v>
       </c>
       <c r="F26" s="10" t="inlineStr">
         <is>
-          <t>AVERIA</t>
-        </is>
-      </c>
-      <c r="G26" s="10" t="inlineStr">
-        <is>
-          <t>522</t>
-        </is>
-      </c>
+          <t>Descuento</t>
+        </is>
+      </c>
+      <c r="G26" s="10" t="inlineStr"/>
       <c r="H26" s="6" t="n">
-        <v>-94983</v>
+        <v>-5220427</v>
       </c>
       <c r="I26" s="11" t="inlineStr">
         <is>
-          <t>AVERIA 4634459674</t>
+          <t>Descuento 85492802</t>
         </is>
       </c>
     </row>
@@ -1208,20 +1176,24 @@
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>85492795</t>
+          <t>85492803</t>
         </is>
       </c>
       <c r="E27" s="6" t="n">
-        <v>-96747</v>
-      </c>
-      <c r="F27" s="10" t="inlineStr"/>
+        <v>-5281206</v>
+      </c>
+      <c r="F27" s="10" t="inlineStr">
+        <is>
+          <t>Descuento</t>
+        </is>
+      </c>
       <c r="G27" s="10" t="inlineStr"/>
       <c r="H27" s="6" t="n">
-        <v>-96747</v>
+        <v>-5281206</v>
       </c>
       <c r="I27" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 85492795</t>
+          <t>Descuento 85492803</t>
         </is>
       </c>
     </row>
@@ -1233,20 +1205,24 @@
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>85492796</t>
+          <t>85492804</t>
         </is>
       </c>
       <c r="E28" s="6" t="n">
-        <v>-400617</v>
-      </c>
-      <c r="F28" s="10" t="inlineStr"/>
+        <v>-8352683</v>
+      </c>
+      <c r="F28" s="10" t="inlineStr">
+        <is>
+          <t>Descuento</t>
+        </is>
+      </c>
       <c r="G28" s="10" t="inlineStr"/>
       <c r="H28" s="6" t="n">
-        <v>-400617</v>
+        <v>-8352683</v>
       </c>
       <c r="I28" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 85492796</t>
+          <t>Descuento 85492804</t>
         </is>
       </c>
     </row>
@@ -1258,20 +1234,24 @@
       </c>
       <c r="D29" s="10" t="inlineStr">
         <is>
-          <t>85492797</t>
+          <t>85492805</t>
         </is>
       </c>
       <c r="E29" s="6" t="n">
-        <v>-773974</v>
-      </c>
-      <c r="F29" s="10" t="inlineStr"/>
+        <v>-13523004</v>
+      </c>
+      <c r="F29" s="10" t="inlineStr">
+        <is>
+          <t>Descuento</t>
+        </is>
+      </c>
       <c r="G29" s="10" t="inlineStr"/>
       <c r="H29" s="6" t="n">
-        <v>-773974</v>
+        <v>-13523004</v>
       </c>
       <c r="I29" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 85492797</t>
+          <t>Descuento 85492805</t>
         </is>
       </c>
     </row>
@@ -1283,20 +1263,24 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>85492798</t>
+          <t>85492806</t>
         </is>
       </c>
       <c r="E30" s="6" t="n">
-        <v>-1762714</v>
-      </c>
-      <c r="F30" s="10" t="inlineStr"/>
+        <v>-18979334</v>
+      </c>
+      <c r="F30" s="10" t="inlineStr">
+        <is>
+          <t>Descuento</t>
+        </is>
+      </c>
       <c r="G30" s="10" t="inlineStr"/>
       <c r="H30" s="6" t="n">
-        <v>-1762714</v>
+        <v>-18979334</v>
       </c>
       <c r="I30" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 85492798</t>
+          <t>Descuento 85492806</t>
         </is>
       </c>
     </row>
@@ -1308,20 +1292,24 @@
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>85492799</t>
+          <t>85492807</t>
         </is>
       </c>
       <c r="E31" s="6" t="n">
-        <v>-2515417</v>
-      </c>
-      <c r="F31" s="10" t="inlineStr"/>
+        <v>-22969880</v>
+      </c>
+      <c r="F31" s="10" t="inlineStr">
+        <is>
+          <t>Descuento</t>
+        </is>
+      </c>
       <c r="G31" s="10" t="inlineStr"/>
       <c r="H31" s="6" t="n">
-        <v>-2515417</v>
+        <v>-22969880</v>
       </c>
       <c r="I31" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 85492799</t>
+          <t>Descuento 85492807</t>
         </is>
       </c>
     </row>
@@ -1333,20 +1321,24 @@
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>85492800</t>
+          <t>85492808</t>
         </is>
       </c>
       <c r="E32" s="6" t="n">
-        <v>-2902404</v>
-      </c>
-      <c r="F32" s="10" t="inlineStr"/>
+        <v>-25545390</v>
+      </c>
+      <c r="F32" s="10" t="inlineStr">
+        <is>
+          <t>Descuento</t>
+        </is>
+      </c>
       <c r="G32" s="10" t="inlineStr"/>
       <c r="H32" s="6" t="n">
-        <v>-2902404</v>
+        <v>-25545390</v>
       </c>
       <c r="I32" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 85492800</t>
+          <t>Descuento 85492808</t>
         </is>
       </c>
     </row>
@@ -1358,20 +1350,24 @@
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>85492801</t>
+          <t>85492809</t>
         </is>
       </c>
       <c r="E33" s="6" t="n">
-        <v>-4125942</v>
-      </c>
-      <c r="F33" s="10" t="inlineStr"/>
+        <v>-66065664</v>
+      </c>
+      <c r="F33" s="10" t="inlineStr">
+        <is>
+          <t>Descuento</t>
+        </is>
+      </c>
       <c r="G33" s="10" t="inlineStr"/>
       <c r="H33" s="6" t="n">
-        <v>-4125942</v>
+        <v>-66065664</v>
       </c>
       <c r="I33" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 85492801</t>
+          <t>Descuento 85492809</t>
         </is>
       </c>
     </row>
@@ -1383,20 +1379,24 @@
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>85492802</t>
+          <t>85492810</t>
         </is>
       </c>
       <c r="E34" s="6" t="n">
-        <v>-5220427</v>
-      </c>
-      <c r="F34" s="10" t="inlineStr"/>
+        <v>-80600110</v>
+      </c>
+      <c r="F34" s="10" t="inlineStr">
+        <is>
+          <t>Descuento</t>
+        </is>
+      </c>
       <c r="G34" s="10" t="inlineStr"/>
       <c r="H34" s="6" t="n">
-        <v>-5220427</v>
+        <v>-80600110</v>
       </c>
       <c r="I34" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 85492802</t>
+          <t>Descuento 85492810</t>
         </is>
       </c>
     </row>
@@ -1408,20 +1408,24 @@
       </c>
       <c r="D35" s="10" t="inlineStr">
         <is>
-          <t>85492803</t>
+          <t>85492811</t>
         </is>
       </c>
       <c r="E35" s="6" t="n">
-        <v>-5281206</v>
-      </c>
-      <c r="F35" s="10" t="inlineStr"/>
+        <v>-111430753</v>
+      </c>
+      <c r="F35" s="10" t="inlineStr">
+        <is>
+          <t>Descuento</t>
+        </is>
+      </c>
       <c r="G35" s="10" t="inlineStr"/>
       <c r="H35" s="6" t="n">
-        <v>-5281206</v>
+        <v>-111430753</v>
       </c>
       <c r="I35" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 85492803</t>
+          <t>Descuento 85492811</t>
         </is>
       </c>
     </row>
@@ -1433,20 +1437,24 @@
       </c>
       <c r="D36" s="10" t="inlineStr">
         <is>
-          <t>85492804</t>
+          <t>85494352</t>
         </is>
       </c>
       <c r="E36" s="6" t="n">
-        <v>-8352683</v>
-      </c>
-      <c r="F36" s="10" t="inlineStr"/>
+        <v>-39949641</v>
+      </c>
+      <c r="F36" s="10" t="inlineStr">
+        <is>
+          <t>Descuento</t>
+        </is>
+      </c>
       <c r="G36" s="10" t="inlineStr"/>
       <c r="H36" s="6" t="n">
-        <v>-8352683</v>
+        <v>-39949641</v>
       </c>
       <c r="I36" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 85492804</t>
+          <t>Descuento 85494352</t>
         </is>
       </c>
     </row>
@@ -1458,20 +1466,24 @@
       </c>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t>85492805</t>
+          <t>85494999</t>
         </is>
       </c>
       <c r="E37" s="6" t="n">
-        <v>-13523004</v>
-      </c>
-      <c r="F37" s="10" t="inlineStr"/>
+        <v>-10000000</v>
+      </c>
+      <c r="F37" s="10" t="inlineStr">
+        <is>
+          <t>Descuento</t>
+        </is>
+      </c>
       <c r="G37" s="10" t="inlineStr"/>
       <c r="H37" s="6" t="n">
-        <v>-13523004</v>
+        <v>-10000000</v>
       </c>
       <c r="I37" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 85492805</t>
+          <t>Descuento 85494999</t>
         </is>
       </c>
     </row>
@@ -1483,20 +1495,24 @@
       </c>
       <c r="D38" s="10" t="inlineStr">
         <is>
-          <t>85492806</t>
+          <t>85495000</t>
         </is>
       </c>
       <c r="E38" s="6" t="n">
-        <v>-18979334</v>
-      </c>
-      <c r="F38" s="10" t="inlineStr"/>
+        <v>-13860888</v>
+      </c>
+      <c r="F38" s="10" t="inlineStr">
+        <is>
+          <t>Descuento</t>
+        </is>
+      </c>
       <c r="G38" s="10" t="inlineStr"/>
       <c r="H38" s="6" t="n">
-        <v>-18979334</v>
+        <v>-13860888</v>
       </c>
       <c r="I38" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 85492806</t>
+          <t>Descuento 85495000</t>
         </is>
       </c>
     </row>
@@ -1508,20 +1524,24 @@
       </c>
       <c r="D39" s="10" t="inlineStr">
         <is>
-          <t>85492807</t>
+          <t>85495001</t>
         </is>
       </c>
       <c r="E39" s="6" t="n">
-        <v>-22969880</v>
-      </c>
-      <c r="F39" s="10" t="inlineStr"/>
+        <v>-25898273</v>
+      </c>
+      <c r="F39" s="10" t="inlineStr">
+        <is>
+          <t>Descuento</t>
+        </is>
+      </c>
       <c r="G39" s="10" t="inlineStr"/>
       <c r="H39" s="6" t="n">
-        <v>-22969880</v>
+        <v>-25898273</v>
       </c>
       <c r="I39" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 85492807</t>
+          <t>Descuento 85495001</t>
         </is>
       </c>
     </row>
@@ -1533,20 +1553,24 @@
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
-          <t>85492808</t>
+          <t>85495002</t>
         </is>
       </c>
       <c r="E40" s="6" t="n">
-        <v>-25545390</v>
-      </c>
-      <c r="F40" s="10" t="inlineStr"/>
+        <v>-386601164</v>
+      </c>
+      <c r="F40" s="10" t="inlineStr">
+        <is>
+          <t>Descuento</t>
+        </is>
+      </c>
       <c r="G40" s="10" t="inlineStr"/>
       <c r="H40" s="6" t="n">
-        <v>-25545390</v>
+        <v>-386601164</v>
       </c>
       <c r="I40" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 85492808</t>
+          <t>Descuento 85495002</t>
         </is>
       </c>
     </row>
@@ -1558,20 +1582,24 @@
       </c>
       <c r="D41" s="10" t="inlineStr">
         <is>
-          <t>85492809</t>
+          <t>85495438</t>
         </is>
       </c>
       <c r="E41" s="6" t="n">
-        <v>-66065664</v>
-      </c>
-      <c r="F41" s="10" t="inlineStr"/>
+        <v>-26648820</v>
+      </c>
+      <c r="F41" s="10" t="inlineStr">
+        <is>
+          <t>Descuento</t>
+        </is>
+      </c>
       <c r="G41" s="10" t="inlineStr"/>
       <c r="H41" s="6" t="n">
-        <v>-66065664</v>
+        <v>-26648820</v>
       </c>
       <c r="I41" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 85492809</t>
+          <t>Descuento 85495438</t>
         </is>
       </c>
     </row>
@@ -1583,20 +1611,24 @@
       </c>
       <c r="D42" s="10" t="inlineStr">
         <is>
-          <t>85492810</t>
+          <t>85495439</t>
         </is>
       </c>
       <c r="E42" s="6" t="n">
-        <v>-80600110</v>
-      </c>
-      <c r="F42" s="10" t="inlineStr"/>
+        <v>-20648820</v>
+      </c>
+      <c r="F42" s="10" t="inlineStr">
+        <is>
+          <t>Descuento</t>
+        </is>
+      </c>
       <c r="G42" s="10" t="inlineStr"/>
       <c r="H42" s="6" t="n">
-        <v>-80600110</v>
+        <v>-20648820</v>
       </c>
       <c r="I42" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 85492810</t>
+          <t>Descuento 85495439</t>
         </is>
       </c>
     </row>
@@ -1608,20 +1640,24 @@
       </c>
       <c r="D43" s="10" t="inlineStr">
         <is>
-          <t>85492811</t>
+          <t>85495673</t>
         </is>
       </c>
       <c r="E43" s="6" t="n">
-        <v>-111430753</v>
-      </c>
-      <c r="F43" s="10" t="inlineStr"/>
+        <v>-13189484</v>
+      </c>
+      <c r="F43" s="10" t="inlineStr">
+        <is>
+          <t>Descuento</t>
+        </is>
+      </c>
       <c r="G43" s="10" t="inlineStr"/>
       <c r="H43" s="6" t="n">
-        <v>-111430753</v>
+        <v>-13189484</v>
       </c>
       <c r="I43" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 85492811</t>
+          <t>Descuento 85495673</t>
         </is>
       </c>
     </row>
@@ -1633,20 +1669,28 @@
       </c>
       <c r="D44" s="10" t="inlineStr">
         <is>
-          <t>85494352</t>
+          <t>4633873108</t>
         </is>
       </c>
       <c r="E44" s="6" t="n">
-        <v>-39949641</v>
-      </c>
-      <c r="F44" s="10" t="inlineStr"/>
-      <c r="G44" s="10" t="inlineStr"/>
+        <v>-57532</v>
+      </c>
+      <c r="F44" s="10" t="inlineStr">
+        <is>
+          <t>AVERIA</t>
+        </is>
+      </c>
+      <c r="G44" s="10" t="inlineStr">
+        <is>
+          <t>522</t>
+        </is>
+      </c>
       <c r="H44" s="6" t="n">
-        <v>-39949641</v>
+        <v>-57532</v>
       </c>
       <c r="I44" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 85494352</t>
+          <t>AVERIA 4633873108</t>
         </is>
       </c>
     </row>
@@ -1658,20 +1702,28 @@
       </c>
       <c r="D45" s="10" t="inlineStr">
         <is>
-          <t>85494999</t>
+          <t>4633966060</t>
         </is>
       </c>
       <c r="E45" s="6" t="n">
-        <v>-10000000</v>
-      </c>
-      <c r="F45" s="10" t="inlineStr"/>
-      <c r="G45" s="10" t="inlineStr"/>
+        <v>-7083</v>
+      </c>
+      <c r="F45" s="10" t="inlineStr">
+        <is>
+          <t>AVERIA</t>
+        </is>
+      </c>
+      <c r="G45" s="10" t="inlineStr">
+        <is>
+          <t>522</t>
+        </is>
+      </c>
       <c r="H45" s="6" t="n">
-        <v>-10000000</v>
+        <v>-7083</v>
       </c>
       <c r="I45" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 85494999</t>
+          <t>AVERIA 4633966060</t>
         </is>
       </c>
     </row>
@@ -1683,20 +1735,28 @@
       </c>
       <c r="D46" s="10" t="inlineStr">
         <is>
-          <t>85495000</t>
+          <t>4634014171</t>
         </is>
       </c>
       <c r="E46" s="6" t="n">
-        <v>-13860888</v>
-      </c>
-      <c r="F46" s="10" t="inlineStr"/>
-      <c r="G46" s="10" t="inlineStr"/>
+        <v>-16320</v>
+      </c>
+      <c r="F46" s="10" t="inlineStr">
+        <is>
+          <t>AVERIA</t>
+        </is>
+      </c>
+      <c r="G46" s="10" t="inlineStr">
+        <is>
+          <t>522</t>
+        </is>
+      </c>
       <c r="H46" s="6" t="n">
-        <v>-13860888</v>
+        <v>-16320</v>
       </c>
       <c r="I46" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 85495000</t>
+          <t>AVERIA 4634014171</t>
         </is>
       </c>
     </row>
@@ -1708,20 +1768,28 @@
       </c>
       <c r="D47" s="10" t="inlineStr">
         <is>
-          <t>85495001</t>
+          <t>4634285011</t>
         </is>
       </c>
       <c r="E47" s="6" t="n">
-        <v>-25898273</v>
-      </c>
-      <c r="F47" s="10" t="inlineStr"/>
-      <c r="G47" s="10" t="inlineStr"/>
+        <v>-106845</v>
+      </c>
+      <c r="F47" s="10" t="inlineStr">
+        <is>
+          <t>AVERIA</t>
+        </is>
+      </c>
+      <c r="G47" s="10" t="inlineStr">
+        <is>
+          <t>522</t>
+        </is>
+      </c>
       <c r="H47" s="6" t="n">
-        <v>-25898273</v>
+        <v>-106845</v>
       </c>
       <c r="I47" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 85495001</t>
+          <t>AVERIA 4634285011</t>
         </is>
       </c>
     </row>
@@ -1733,20 +1801,28 @@
       </c>
       <c r="D48" s="10" t="inlineStr">
         <is>
-          <t>85495002</t>
+          <t>4634301618</t>
         </is>
       </c>
       <c r="E48" s="6" t="n">
-        <v>-386601164</v>
-      </c>
-      <c r="F48" s="10" t="inlineStr"/>
-      <c r="G48" s="10" t="inlineStr"/>
+        <v>-16809</v>
+      </c>
+      <c r="F48" s="10" t="inlineStr">
+        <is>
+          <t>AVERIA</t>
+        </is>
+      </c>
+      <c r="G48" s="10" t="inlineStr">
+        <is>
+          <t>522</t>
+        </is>
+      </c>
       <c r="H48" s="6" t="n">
-        <v>-386601164</v>
+        <v>-16809</v>
       </c>
       <c r="I48" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 85495002</t>
+          <t>AVERIA 4634301618</t>
         </is>
       </c>
     </row>
@@ -1758,20 +1834,28 @@
       </c>
       <c r="D49" s="10" t="inlineStr">
         <is>
-          <t>85495438</t>
+          <t>4634328866</t>
         </is>
       </c>
       <c r="E49" s="6" t="n">
-        <v>-26648820</v>
-      </c>
-      <c r="F49" s="10" t="inlineStr"/>
-      <c r="G49" s="10" t="inlineStr"/>
+        <v>-14166</v>
+      </c>
+      <c r="F49" s="10" t="inlineStr">
+        <is>
+          <t>AVERIA</t>
+        </is>
+      </c>
+      <c r="G49" s="10" t="inlineStr">
+        <is>
+          <t>522</t>
+        </is>
+      </c>
       <c r="H49" s="6" t="n">
-        <v>-26648820</v>
+        <v>-14166</v>
       </c>
       <c r="I49" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 85495438</t>
+          <t>AVERIA 4634328866</t>
         </is>
       </c>
     </row>
@@ -1783,20 +1867,28 @@
       </c>
       <c r="D50" s="10" t="inlineStr">
         <is>
-          <t>85495439</t>
+          <t>4634412628</t>
         </is>
       </c>
       <c r="E50" s="6" t="n">
-        <v>-20648820</v>
-      </c>
-      <c r="F50" s="10" t="inlineStr"/>
-      <c r="G50" s="10" t="inlineStr"/>
+        <v>-16320</v>
+      </c>
+      <c r="F50" s="10" t="inlineStr">
+        <is>
+          <t>AVERIA</t>
+        </is>
+      </c>
+      <c r="G50" s="10" t="inlineStr">
+        <is>
+          <t>522</t>
+        </is>
+      </c>
       <c r="H50" s="6" t="n">
-        <v>-20648820</v>
+        <v>-16320</v>
       </c>
       <c r="I50" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 85495439</t>
+          <t>AVERIA 4634412628</t>
         </is>
       </c>
     </row>
@@ -1808,20 +1900,28 @@
       </c>
       <c r="D51" s="10" t="inlineStr">
         <is>
-          <t>85495673</t>
+          <t>4634459674</t>
         </is>
       </c>
       <c r="E51" s="6" t="n">
-        <v>-13189484</v>
-      </c>
-      <c r="F51" s="10" t="inlineStr"/>
-      <c r="G51" s="10" t="inlineStr"/>
+        <v>-94983</v>
+      </c>
+      <c r="F51" s="10" t="inlineStr">
+        <is>
+          <t>AVERIA</t>
+        </is>
+      </c>
+      <c r="G51" s="10" t="inlineStr">
+        <is>
+          <t>522</t>
+        </is>
+      </c>
       <c r="H51" s="6" t="n">
-        <v>-13189484</v>
+        <v>-94983</v>
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 85495673</t>
+          <t>AVERIA 4634459674</t>
         </is>
       </c>
     </row>
